--- a/public/data/contract_insurance.xlsx
+++ b/public/data/contract_insurance.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>05b403ed-56f4-4920-9d7a-d216173041ba</v>
+        <v>b849968c-c12c-410d-919e-011849ceb220</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -442,21 +442,21 @@
         <v>Yes</v>
       </c>
       <c r="G2" t="str">
-        <v>Included in transfer fare</v>
+        <v>Included in fare</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>daec19a6-71d0-4314-967e-f9f226b1b5fc</v>
+        <v>be40e6c9-1fe7-46f3-950c-56af609cf921</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E3" t="str">
         <v>Insurance cover</v>
@@ -465,21 +465,21 @@
         <v>Yes</v>
       </c>
       <c r="G3" t="str">
-        <v>Basic cover included</v>
+        <v>Standard cover</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>10e22acc-2225-4dfc-a99b-1edc4ab6b494</v>
+        <v>4b7b502a-77fc-4733-add4-18291cdf6844</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E4" t="str">
         <v>Insurance cover</v>
@@ -488,21 +488,21 @@
         <v>Yes</v>
       </c>
       <c r="G4" t="str">
-        <v>Charter insurance included</v>
+        <v>Standard cover</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>860eff79-6615-4034-940f-122cae3e1eb0</v>
+        <v>de9366ca-d8fa-4889-9b9f-32fd19d7da1f</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-004-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E5" t="str">
         <v>Insurance cover</v>
@@ -511,21 +511,21 @@
         <v>Yes</v>
       </c>
       <c r="G5" t="str">
-        <v>Comprehensive cover</v>
+        <v>Included in fare</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>b6a78cc9-6b28-4326-9967-72a3a5b04607</v>
+        <v>92d0ace3-91ca-48e9-ad85-05ac12c849e9</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E6" t="str">
         <v>Insurance cover</v>
@@ -539,16 +539,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1f4db1e6-c042-4500-a732-c5c82a1b39e3</v>
+        <v>0226721c-9b76-41c0-b8cc-7d49781a43b7</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E7" t="str">
         <v>Insurance cover</v>
@@ -557,21 +557,21 @@
         <v>Yes</v>
       </c>
       <c r="G7" t="str">
-        <v>Full coverage per TMA policy</v>
+        <v>Included in fare</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>124b1728-8a01-4afe-b5ce-dfa29d256945</v>
+        <v>ccded64d-a555-48b5-bdb4-3f4338527b22</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E8" t="str">
         <v>Insurance cover</v>
@@ -580,21 +580,21 @@
         <v>Yes</v>
       </c>
       <c r="G8" t="str">
-        <v>Speedboat insurance included</v>
+        <v>Included in fare</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6ae390c8-9a12-4d11-8fe0-81875deae990</v>
+        <v>7e6d746e-196f-4e00-bd53-ac07c818fdb2</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E9" t="str">
         <v>Insurance cover</v>
@@ -603,21 +603,21 @@
         <v>Yes</v>
       </c>
       <c r="G9" t="str">
-        <v>Charter insurance included</v>
+        <v>Included in fare</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5efaeef4-209a-4bbb-a4a0-09f9c274f4c7</v>
+        <v>4712cb71-e3a8-45a7-9882-3991befb6dab</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E10" t="str">
         <v>Insurance cover</v>
@@ -626,35 +626,242 @@
         <v>Yes</v>
       </c>
       <c r="G10" t="str">
-        <v>Marine transit coverage</v>
+        <v>Standard cover</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>80846643-df0c-4a41-a9ec-049625325d39</v>
+        <v>d4d1ee88-a512-4a8b-bca2-0e19dd18a0ce</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Included in fare</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>a7f10841-45ae-47ef-8c0b-602b37abc5b2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Standard cover</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>07833196-7bf9-4fd3-9d87-b26493174609</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Included in fare</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4c7dfe88-8da7-4ca5-9d50-e65005870c50</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Marine transit coverage</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>8537cc7b-dc89-4188-8886-41b65876c27a</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Marine transit coverage</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>714484e4-1a96-4928-a961-c881076b2c10</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Included in fare</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>7c3aadf3-3003-4d4d-9e0b-761a39f9281e</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Standard cover</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>6df1ca0a-adc7-4356-8836-1560dc76d615</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Included in fare</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4e19c577-4b93-4bd1-8321-06eda109cd06</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="E11" t="str">
-        <v>Insurance cover</v>
-      </c>
-      <c r="F11" t="str">
+      <c r="E19" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F19" t="str">
         <v>No</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G19" t="str">
         <v>Resort arranges own cover</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>c0d63f15-cae8-4321-b4ae-2067fb49e95d</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Insurance cover</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Included in fare</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
   </ignoredErrors>
 </worksheet>
 </file>